--- a/sheets/조재수대금교본/검수/인연-2.xlsx
+++ b/sheets/조재수대금교본/검수/인연-2.xlsx
@@ -4469,7 +4469,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -4480,11 +4480,7 @@
         </is>
       </c>
       <c r="Q3" s="22"/>
-      <c r="R3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R3" s="21"/>
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
@@ -4502,7 +4498,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∧
+          <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
@@ -4549,14 +4545,13 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -4568,8 +4563,7 @@
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼
-‹</t>
+          <t xml:space="preserve">湳∼</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -4579,16 +4573,11 @@
         </is>
       </c>
       <c r="M5" s="24"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="Q5" s="24"/>
@@ -4604,11 +4593,7 @@
     </row>
     <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
@@ -4621,8 +4606,7 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹ﾉ</t>
+㳞</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -4636,8 +4620,7 @@
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -4650,9 +4633,8 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ﾉ
-–
-仲林∧</t>
+          <t xml:space="preserve">–
+仲林</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4694,13 +4676,13 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -4719,7 +4701,7 @@
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∽</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -4793,24 +4775,15 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G9" s="22"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H9" s="21"/>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
@@ -4826,11 +4799,7 @@
         </is>
       </c>
       <c r="O9" s="22"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
@@ -4859,8 +4828,7 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ﾉ
-–
+          <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
@@ -4879,16 +4847,11 @@
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O10" s="23"/>
@@ -4902,8 +4865,7 @@
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="S10" s="23"/>
@@ -4932,7 +4894,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4944,7 +4906,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K11" s="24"/>
@@ -4956,13 +4918,13 @@
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -5032,11 +4994,7 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
@@ -5045,11 +5003,7 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -5058,11 +5012,7 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
@@ -5070,11 +5020,7 @@
         </is>
       </c>
       <c r="Q13" s="23"/>
-      <c r="R13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R13" s="21"/>
       <c r="S13" s="23"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
@@ -5086,17 +5032,11 @@
     </row>
     <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-ﾉ
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -5280,11 +5220,7 @@
       <c r="Q20" s="22"/>
       <c r="R20" s="21"/>
       <c r="S20" s="22"/>
-      <c r="T20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
     <row r="21" ht="119.22" customHeight="true">
@@ -5417,11 +5353,7 @@
       <c r="Q25" s="24"/>
       <c r="R25" s="21"/>
       <c r="S25" s="24"/>
-      <c r="T25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
     <row r="26" ht="119.22" customHeight="true">
@@ -5446,7 +5378,7 @@
       <c r="S26" s="22"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅋ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U26" s="22"/>
@@ -5496,7 +5428,7 @@
       <c r="S28" s="24"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ㅂ
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/인연-2.xlsx
+++ b/sheets/조재수대금교본/검수/인연-2.xlsx
@@ -4469,7 +4469,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -4480,7 +4480,11 @@
         </is>
       </c>
       <c r="Q3" s="22"/>
-      <c r="R3" s="21"/>
+      <c r="R3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
@@ -4498,7 +4502,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳∧
 –</t>
         </is>
       </c>
@@ -4551,7 +4555,7 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -4606,7 +4610,8 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -4633,8 +4638,9 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲林</t>
+          <t xml:space="preserve">ﾉ
+–
+仲林∧</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4676,13 +4682,13 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -4701,7 +4707,7 @@
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲∽</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -4779,7 +4785,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -4828,7 +4834,8 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">ﾉ
+–
 汰潢</t>
         </is>
       </c>
@@ -4851,7 +4858,8 @@
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="O10" s="23"/>
@@ -4894,7 +4902,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4906,7 +4914,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="K11" s="24"/>
@@ -4918,13 +4926,13 @@
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -5020,7 +5028,11 @@
         </is>
       </c>
       <c r="Q13" s="23"/>
-      <c r="R13" s="21"/>
+      <c r="R13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S13" s="23"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
@@ -5036,7 +5048,8 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞
+ﾉ</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -5378,7 +5391,7 @@
       <c r="S26" s="22"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅋ</t>
         </is>
       </c>
       <c r="U26" s="22"/>
@@ -5428,7 +5441,7 @@
       <c r="S28" s="24"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–ㅂ
 △</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/인연-2.xlsx
+++ b/sheets/조재수대금교본/검수/인연-2.xlsx
@@ -4376,32 +4376,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="80.0" customHeight="true">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="119.22" customHeight="true">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="119.22" customHeight="true">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="119.22" customHeight="true">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="119.22" customHeight="true">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="119.22" customHeight="true">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="119.22" customHeight="true">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="119.22" customHeight="true">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4816,7 +4816,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="119.22" customHeight="true">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="119.22" customHeight="true">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="119.22" customHeight="true">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="119.22" customHeight="true">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="119.22" customHeight="true">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -5113,7 +5113,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="80.0" customHeight="true">
+    <row r="16" ht="93.02" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="119.22" customHeight="true">
+    <row r="17" ht="138.71" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="119.22" customHeight="true">
+    <row r="18" ht="138.71" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5190,7 +5190,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="119.22" customHeight="true">
+    <row r="19" ht="138.71" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5213,7 +5213,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="119.22" customHeight="true">
+    <row r="20" ht="138.71" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -5236,7 +5236,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="119.22" customHeight="true">
+    <row r="21" ht="138.71" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="119.22" customHeight="true">
+    <row r="22" ht="138.71" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="119.22" customHeight="true">
+    <row r="23" ht="138.71" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="119.22" customHeight="true">
+    <row r="24" ht="138.71" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="119.22" customHeight="true">
+    <row r="25" ht="138.71" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -5369,7 +5369,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="119.22" customHeight="true">
+    <row r="26" ht="138.71" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="119.22" customHeight="true">
+    <row r="27" ht="138.71" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -5419,7 +5419,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="119.22" customHeight="true">
+    <row r="28" ht="138.71" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5454,7 +5454,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
